--- a/DOCS/G1_Requerimientos_CareStock.xlsx
+++ b/DOCS/G1_Requerimientos_CareStock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C8DBAD-AE77-40FC-905F-B6EC06992F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9796B4E0-1FC9-4AEC-B4D5-FBD30DCFA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="746" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="746" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actores" sheetId="3" r:id="rId1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
   <si>
     <t>Descripción</t>
   </si>
@@ -643,13 +643,7 @@
     </r>
   </si>
   <si>
-    <t>Funcional</t>
-  </si>
-  <si>
-    <t>Rendimiento</t>
-  </si>
-  <si>
-    <t>Usabilidad</t>
+    <t>sfsdfsdf</t>
   </si>
 </sst>
 </file>
@@ -657,7 +651,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="37" x14ac:knownFonts="1">
     <font>
@@ -1477,7 +1471,7 @@
     <xf numFmtId="0" fontId="35" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1946,15 +1940,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="59.7109375" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="59.6640625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="4" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
@@ -1962,17 +1956,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
     </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
@@ -1983,7 +1977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
@@ -1994,63 +1988,63 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
     </row>
-    <row r="7" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
     </row>
-    <row r="9" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
     </row>
-    <row r="10" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
     </row>
-    <row r="11" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
     </row>
-    <row r="12" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
     </row>
-    <row r="13" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
     </row>
-    <row r="14" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>15</v>
       </c>
@@ -2073,14 +2067,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="76.28515625" customWidth="1"/>
+    <col min="3" max="3" width="76.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="18" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="18" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>19</v>
       </c>
@@ -2088,17 +2082,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="15.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>43</v>
       </c>
@@ -2109,70 +2103,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
     </row>
-    <row r="6" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="20"/>
     </row>
-    <row r="7" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
     </row>
-    <row r="8" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>28</v>
       </c>
@@ -2195,20 +2189,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="88.5703125" style="36" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="88.5546875" style="36" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="36" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" style="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" style="36" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" style="36" customWidth="1"/>
-    <col min="7" max="11" width="14.7109375" style="41" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.85546875" style="36"/>
+    <col min="6" max="6" width="32.6640625" style="36" customWidth="1"/>
+    <col min="7" max="11" width="14.6640625" style="41" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.88671875" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>29</v>
       </c>
@@ -2223,7 +2217,7 @@
       <c r="J1" s="77"/>
       <c r="K1" s="78"/>
     </row>
-    <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>3</v>
       </c>
@@ -2233,7 +2227,7 @@
       <c r="J2" s="80"/>
       <c r="K2" s="81"/>
     </row>
-    <row r="3" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37"/>
       <c r="G3" s="67" t="s">
         <v>44</v>
@@ -2243,7 +2237,7 @@
       <c r="J3" s="68"/>
       <c r="K3" s="69"/>
     </row>
-    <row r="4" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="G4" s="70"/>
       <c r="H4" s="71"/>
@@ -2251,7 +2245,7 @@
       <c r="J4" s="71"/>
       <c r="K4" s="72"/>
     </row>
-    <row r="5" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
       <c r="G5" s="73"/>
       <c r="H5" s="74"/>
@@ -2259,7 +2253,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="75"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="65"/>
@@ -2272,7 +2266,7 @@
       <c r="J6" s="65"/>
       <c r="K6" s="66"/>
     </row>
-    <row r="7" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>47</v>
       </c>
@@ -2307,7 +2301,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="38" customFormat="1" ht="169.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" s="38" customFormat="1" ht="169.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>45</v>
       </c>
@@ -2340,7 +2334,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>30</v>
       </c>
@@ -2365,7 +2359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>31</v>
       </c>
@@ -2380,11 +2374,13 @@
       <c r="J10" s="53"/>
       <c r="K10" s="54"/>
     </row>
-    <row r="11" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="61" t="s">
+        <v>78</v>
+      </c>
       <c r="C11" s="61"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -2395,7 +2391,7 @@
       <c r="J11" s="53"/>
       <c r="K11" s="54"/>
     </row>
-    <row r="12" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>33</v>
       </c>
@@ -2410,23 +2406,21 @@
       <c r="J12" s="53"/>
       <c r="K12" s="54"/>
     </row>
-    <row r="13" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="61" t="s">
-        <v>78</v>
-      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="50"/>
       <c r="H13" s="51"/>
       <c r="I13" s="52"/>
       <c r="J13" s="53"/>
       <c r="K13" s="54"/>
     </row>
-    <row r="14" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>35</v>
       </c>
@@ -2434,16 +2428,14 @@
       <c r="C14" s="61"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="61" t="s">
-        <v>78</v>
-      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="52"/>
       <c r="J14" s="53"/>
       <c r="K14" s="54"/>
     </row>
-    <row r="15" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>36</v>
       </c>
@@ -2451,16 +2443,14 @@
       <c r="C15" s="61"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="61" t="s">
-        <v>79</v>
-      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="52"/>
       <c r="J15" s="53"/>
       <c r="K15" s="54"/>
     </row>
-    <row r="16" spans="1:11" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>37</v>
       </c>
@@ -2468,16 +2458,14 @@
       <c r="C16" s="61"/>
       <c r="D16" s="40"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="61" t="s">
-        <v>80</v>
-      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="52"/>
       <c r="J16" s="53"/>
       <c r="K16" s="54"/>
     </row>
-    <row r="17" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>38</v>
       </c>
@@ -2491,7 +2479,7 @@
       <c r="J17" s="53"/>
       <c r="K17" s="54"/>
     </row>
-    <row r="18" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>18</v>
       </c>
@@ -2506,7 +2494,7 @@
       <c r="J18" s="53"/>
       <c r="K18" s="54"/>
     </row>
-    <row r="19" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>57</v>
       </c>
@@ -2521,7 +2509,7 @@
       <c r="J19" s="53"/>
       <c r="K19" s="54"/>
     </row>
-    <row r="20" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>58</v>
       </c>
@@ -2536,7 +2524,7 @@
       <c r="J20" s="53"/>
       <c r="K20" s="54"/>
     </row>
-    <row r="21" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>59</v>
       </c>
@@ -2551,7 +2539,7 @@
       <c r="J21" s="53"/>
       <c r="K21" s="54"/>
     </row>
-    <row r="22" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>60</v>
       </c>
@@ -2566,7 +2554,7 @@
       <c r="J22" s="53"/>
       <c r="K22" s="54"/>
     </row>
-    <row r="23" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>61</v>
       </c>
@@ -2581,7 +2569,7 @@
       <c r="J23" s="53"/>
       <c r="K23" s="54"/>
     </row>
-    <row r="24" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>70</v>
       </c>
@@ -2596,7 +2584,7 @@
       <c r="J24" s="53"/>
       <c r="K24" s="54"/>
     </row>
-    <row r="25" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>71</v>
       </c>
@@ -2611,7 +2599,7 @@
       <c r="J25" s="53"/>
       <c r="K25" s="54"/>
     </row>
-    <row r="26" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>72</v>
       </c>
@@ -2626,7 +2614,7 @@
       <c r="J26" s="53"/>
       <c r="K26" s="54"/>
     </row>
-    <row r="27" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>73</v>
       </c>
@@ -2641,7 +2629,7 @@
       <c r="J27" s="53"/>
       <c r="K27" s="54"/>
     </row>
-    <row r="28" spans="1:12" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="49.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
         <v>74</v>
       </c>
@@ -2656,7 +2644,7 @@
       <c r="J28" s="58"/>
       <c r="K28" s="59"/>
     </row>
-    <row r="29" spans="1:12" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G29" s="48">
         <f>AVERAGE(G9:G28)</f>
         <v>0</v>
@@ -2682,57 +2670,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
       <c r="I30" s="36"/>
       <c r="J30" s="36"/>
       <c r="K30" s="36"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G31" s="36"/>
       <c r="H31" s="36"/>
       <c r="I31" s="36"/>
       <c r="J31" s="36"/>
       <c r="K31" s="36"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G32" s="36"/>
       <c r="H32" s="36"/>
       <c r="I32" s="36"/>
       <c r="J32" s="36"/>
       <c r="K32" s="36"/>
     </row>
-    <row r="33" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="36" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="33" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A6:K6"/>

--- a/DOCS/G1_Requerimientos_CareStock.xlsx
+++ b/DOCS/G1_Requerimientos_CareStock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9796B4E0-1FC9-4AEC-B4D5-FBD30DCFA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3675EE6E-184C-4E50-9822-C7265F9C21A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="746" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>Descripción</t>
   </si>
@@ -641,9 +641,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>sfsdfsdf</t>
   </si>
 </sst>
 </file>
@@ -2378,9 +2375,7 @@
       <c r="A11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="61" t="s">
-        <v>78</v>
-      </c>
+      <c r="B11" s="61"/>
       <c r="C11" s="61"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
